--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BB52097-991A-4FFB-8436-65A05DDD379A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3702C47D-E48B-4E05-82ED-43FF71D42061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3702C47D-E48B-4E05-82ED-43FF71D42061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{944808CF-3573-4FEE-B633-EDA408FD3B17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="60">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1086,26 +1086,50 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+      <c r="A8" s="13">
+        <v>46246</v>
+      </c>
+      <c r="B8" s="14">
+        <v>350</v>
+      </c>
+      <c r="C8" s="14">
+        <v>30</v>
+      </c>
+      <c r="D8" s="14">
+        <v>20</v>
+      </c>
+      <c r="E8" s="14">
+        <v>120</v>
+      </c>
+      <c r="F8" s="14">
+        <v>350</v>
+      </c>
+      <c r="G8" s="14">
+        <v>7</v>
+      </c>
+      <c r="H8" s="14">
+        <v>50</v>
+      </c>
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>920</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="17"/>
+        <v>520</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{944808CF-3573-4FEE-B633-EDA408FD3B17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F30F08A7-8BF8-4953-AE70-A7432EA6C06D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -215,6 +215,12 @@
   </si>
   <si>
     <t>Heavy Lecture day.</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Filling netural</t>
   </si>
 </sst>
 </file>
@@ -1132,26 +1138,50 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+      <c r="A9" s="13">
+        <v>46247</v>
+      </c>
+      <c r="B9" s="14">
+        <v>480</v>
+      </c>
+      <c r="C9" s="14">
+        <v>15</v>
+      </c>
+      <c r="D9" s="14">
+        <v>90</v>
+      </c>
+      <c r="E9" s="14">
+        <v>40</v>
+      </c>
+      <c r="F9" s="14">
+        <v>150</v>
+      </c>
+      <c r="G9" s="14">
+        <v>3</v>
+      </c>
+      <c r="H9" s="14">
+        <v>180</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>955</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
+        <v>485</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F30F08A7-8BF8-4953-AE70-A7432EA6C06D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2512E50-A85B-4FC3-8187-DAFF40543640}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1184,26 +1184,50 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+      <c r="A10" s="13">
+        <v>46248</v>
+      </c>
+      <c r="B10" s="14">
+        <v>340</v>
+      </c>
+      <c r="C10" s="14">
+        <v>30</v>
+      </c>
+      <c r="D10" s="14">
+        <v>120</v>
+      </c>
+      <c r="E10" s="14">
+        <v>50</v>
+      </c>
+      <c r="F10" s="14">
+        <v>300</v>
+      </c>
+      <c r="G10" s="14">
+        <v>6</v>
+      </c>
+      <c r="H10" s="14">
+        <v>250</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
+        <v>350</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2512E50-A85B-4FC3-8187-DAFF40543640}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B879222C-4D2C-4F94-B999-10F15DD09DB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -221,6 +221,12 @@
   </si>
   <si>
     <t>Filling netural</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>I am feeling good this day</t>
   </si>
 </sst>
 </file>
@@ -1230,26 +1236,50 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="A11" s="13">
+        <v>46249</v>
+      </c>
+      <c r="B11" s="14">
+        <v>600</v>
+      </c>
+      <c r="C11" s="14">
+        <v>20</v>
+      </c>
+      <c r="D11" s="14">
+        <v>50</v>
+      </c>
+      <c r="E11" s="14">
+        <v>15</v>
+      </c>
+      <c r="F11" s="14">
+        <v>0</v>
+      </c>
+      <c r="G11" s="14">
+        <v>0</v>
+      </c>
+      <c r="H11" s="14">
+        <v>160</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>845</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
+        <v>595</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B879222C-4D2C-4F94-B999-10F15DD09DB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9224874-FC6C-40E2-954C-6859C925801C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -227,6 +227,9 @@
   </si>
   <si>
     <t>I am feeling good this day</t>
+  </si>
+  <si>
+    <t>today something new  learning,like comminaction skill</t>
   </si>
 </sst>
 </file>
@@ -1281,27 +1284,51 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+    <row r="12" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A12" s="13">
+        <v>46250</v>
+      </c>
+      <c r="B12" s="14">
+        <v>600</v>
+      </c>
+      <c r="C12" s="14">
+        <v>10</v>
+      </c>
+      <c r="D12" s="14">
+        <v>80</v>
+      </c>
+      <c r="E12" s="14">
+        <v>30</v>
+      </c>
+      <c r="F12" s="14">
+        <v>0</v>
+      </c>
+      <c r="G12" s="14">
+        <v>0</v>
+      </c>
+      <c r="H12" s="14">
+        <v>300</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
+        <v>420</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9224874-FC6C-40E2-954C-6859C925801C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C2DB8FD-7D6F-4334-8386-BC50EF2052B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -230,6 +230,9 @@
   </si>
   <si>
     <t>today something new  learning,like comminaction skill</t>
+  </si>
+  <si>
+    <t>feeling good</t>
   </si>
 </sst>
 </file>
@@ -1331,26 +1334,50 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="13">
+        <v>46251</v>
+      </c>
+      <c r="B13" s="14">
+        <v>480</v>
+      </c>
+      <c r="C13" s="14">
+        <v>25</v>
+      </c>
+      <c r="D13" s="14">
+        <v>200</v>
+      </c>
+      <c r="E13" s="14">
+        <v>35</v>
+      </c>
+      <c r="F13" s="14">
+        <v>350</v>
+      </c>
+      <c r="G13" s="14">
+        <v>7</v>
+      </c>
+      <c r="H13" s="14">
+        <v>200</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>1290</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+        <v>150</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C2DB8FD-7D6F-4334-8386-BC50EF2052B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8D2BB16-B19D-429D-AA25-68910E0B8D13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -233,6 +233,12 @@
   </si>
   <si>
     <t>feeling good</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Very good feeling today</t>
   </si>
 </sst>
 </file>
@@ -1380,26 +1386,50 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="A14" s="13">
+        <v>46252</v>
+      </c>
+      <c r="B14" s="14">
+        <v>420</v>
+      </c>
+      <c r="C14" s="14">
+        <v>30</v>
+      </c>
+      <c r="D14" s="14">
+        <v>120</v>
+      </c>
+      <c r="E14" s="14">
+        <v>45</v>
+      </c>
+      <c r="F14" s="14">
+        <v>200</v>
+      </c>
+      <c r="G14" s="14">
+        <v>4</v>
+      </c>
+      <c r="H14" s="14">
+        <v>180</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>995</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+        <v>445</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8D2BB16-B19D-429D-AA25-68910E0B8D13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B99B5ACF-495B-410B-8ADE-0DC82B0F5E0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1432,26 +1432,50 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="A15" s="13">
+        <v>46253</v>
+      </c>
+      <c r="B15" s="14">
+        <v>400</v>
+      </c>
+      <c r="C15" s="14">
+        <v>10</v>
+      </c>
+      <c r="D15" s="14">
+        <v>120</v>
+      </c>
+      <c r="E15" s="14">
+        <v>30</v>
+      </c>
+      <c r="F15" s="14">
+        <v>350</v>
+      </c>
+      <c r="G15" s="14">
+        <v>7</v>
+      </c>
+      <c r="H15" s="14">
+        <v>200</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>330</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B99B5ACF-495B-410B-8ADE-0DC82B0F5E0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3275319F-162D-4F1C-9D66-319A935B840D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1478,26 +1478,50 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="A16" s="13">
+        <v>46254</v>
+      </c>
+      <c r="B16" s="14">
+        <v>430</v>
+      </c>
+      <c r="C16" s="14">
+        <v>20</v>
+      </c>
+      <c r="D16" s="14">
+        <v>50</v>
+      </c>
+      <c r="E16" s="14">
+        <v>25</v>
+      </c>
+      <c r="F16" s="14">
+        <v>100</v>
+      </c>
+      <c r="G16" s="14">
+        <v>2</v>
+      </c>
+      <c r="H16" s="14">
+        <v>250</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>875</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+        <v>565</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3275319F-162D-4F1C-9D66-319A935B840D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD32CFA7-B3B9-4A17-8888-6F78A5A7A56A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -239,6 +239,9 @@
   </si>
   <si>
     <t>Very good feeling today</t>
+  </si>
+  <si>
+    <t>good</t>
   </si>
 </sst>
 </file>
@@ -1524,26 +1527,50 @@
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="13">
+        <v>46255</v>
+      </c>
+      <c r="B17" s="14">
+        <v>450</v>
+      </c>
+      <c r="C17" s="14">
+        <v>10</v>
+      </c>
+      <c r="D17" s="14">
+        <v>40</v>
+      </c>
+      <c r="E17" s="14">
+        <v>50</v>
+      </c>
+      <c r="F17" s="14">
+        <v>300</v>
+      </c>
+      <c r="G17" s="14">
+        <v>6</v>
+      </c>
+      <c r="H17" s="14">
+        <v>220</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>370</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD32CFA7-B3B9-4A17-8888-6F78A5A7A56A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCB2CD49-565B-4BE5-A20A-0B537BBD0EE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -242,6 +242,9 @@
   </si>
   <si>
     <t>good</t>
+  </si>
+  <si>
+    <t>good feeling</t>
   </si>
 </sst>
 </file>
@@ -1573,26 +1576,50 @@
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="13">
+        <v>46256</v>
+      </c>
+      <c r="B18" s="14">
+        <v>300</v>
+      </c>
+      <c r="C18" s="14">
+        <v>30</v>
+      </c>
+      <c r="D18" s="14">
+        <v>120</v>
+      </c>
+      <c r="E18" s="14">
+        <v>45</v>
+      </c>
+      <c r="F18" s="14">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14">
+        <v>0</v>
+      </c>
+      <c r="H18" s="14">
+        <v>300</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>795</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>645</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCB2CD49-565B-4BE5-A20A-0B537BBD0EE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19418FAA-D61D-4470-865D-921AA475720A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1622,26 +1622,50 @@
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13">
+        <v>46257</v>
+      </c>
+      <c r="B19" s="14">
+        <v>400</v>
+      </c>
+      <c r="C19" s="14">
+        <v>30</v>
+      </c>
+      <c r="D19" s="14">
+        <v>30</v>
+      </c>
+      <c r="E19" s="14">
+        <v>20</v>
+      </c>
+      <c r="F19" s="14">
+        <v>0</v>
+      </c>
+      <c r="G19" s="14">
+        <v>0</v>
+      </c>
+      <c r="H19" s="14">
+        <v>360</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>840</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>600</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19418FAA-D61D-4470-865D-921AA475720A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B57CA006-33B0-4757-8092-DEB1FDAD2A3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -245,6 +245,9 @@
   </si>
   <si>
     <t>good feeling</t>
+  </si>
+  <si>
+    <t>feeling bad</t>
   </si>
 </sst>
 </file>
@@ -1668,26 +1671,50 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="A20" s="13">
+        <v>46258</v>
+      </c>
+      <c r="B20" s="14">
+        <v>480</v>
+      </c>
+      <c r="C20" s="14">
+        <v>20</v>
+      </c>
+      <c r="D20" s="14">
+        <v>45</v>
+      </c>
+      <c r="E20" s="14">
+        <v>30</v>
+      </c>
+      <c r="F20" s="14">
+        <v>300</v>
+      </c>
+      <c r="G20" s="14">
+        <v>6</v>
+      </c>
+      <c r="H20" s="14">
+        <v>260</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>1135</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>305</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B57CA006-33B0-4757-8092-DEB1FDAD2A3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8AD5CAB-F664-446F-9CAB-55860CDEE4BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1717,26 +1717,50 @@
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="A21" s="13">
+        <v>46259</v>
+      </c>
+      <c r="B21" s="14">
+        <v>390</v>
+      </c>
+      <c r="C21" s="14">
+        <v>30</v>
+      </c>
+      <c r="D21" s="14">
+        <v>45</v>
+      </c>
+      <c r="E21" s="14">
+        <v>60</v>
+      </c>
+      <c r="F21" s="14">
+        <v>350</v>
+      </c>
+      <c r="G21" s="14">
+        <v>7</v>
+      </c>
+      <c r="H21" s="14">
+        <v>200</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>1075</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>365</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8AD5CAB-F664-446F-9CAB-55860CDEE4BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B43BC52-6998-4C7B-AE18-43B879E36EAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1763,26 +1763,50 @@
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="A22" s="13">
+        <v>46260</v>
+      </c>
+      <c r="B22" s="14">
+        <v>390</v>
+      </c>
+      <c r="C22" s="14">
+        <v>10</v>
+      </c>
+      <c r="D22" s="14">
+        <v>20</v>
+      </c>
+      <c r="E22" s="14">
+        <v>40</v>
+      </c>
+      <c r="F22" s="14">
+        <v>300</v>
+      </c>
+      <c r="G22" s="14">
+        <v>6</v>
+      </c>
+      <c r="H22" s="14">
+        <v>300</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>380</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B43BC52-6998-4C7B-AE18-43B879E36EAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72CED644-9DF7-4EC6-9CEB-65C93ED38B7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -248,6 +248,9 @@
   </si>
   <si>
     <t>feeling bad</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
   </si>
 </sst>
 </file>
@@ -1809,26 +1812,50 @@
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="A23" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B23" s="14">
+        <v>400</v>
+      </c>
+      <c r="C23" s="14">
+        <v>20</v>
+      </c>
+      <c r="D23" s="14">
+        <v>30</v>
+      </c>
+      <c r="E23" s="14">
+        <v>20</v>
+      </c>
+      <c r="F23" s="14">
+        <v>200</v>
+      </c>
+      <c r="G23" s="14">
+        <v>4</v>
+      </c>
+      <c r="H23" s="14">
+        <v>260</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+        <v>510</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72CED644-9DF7-4EC6-9CEB-65C93ED38B7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBA958D2-E0C4-4AF0-B87C-EB7BB36D054C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -251,6 +251,9 @@
   </si>
   <si>
     <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>today something new  learning</t>
   </si>
 </sst>
 </file>
@@ -1858,26 +1861,50 @@
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="A24" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B24" s="14">
+        <v>380</v>
+      </c>
+      <c r="C24" s="14">
+        <v>20</v>
+      </c>
+      <c r="D24" s="14">
+        <v>120</v>
+      </c>
+      <c r="E24" s="14">
+        <v>40</v>
+      </c>
+      <c r="F24" s="14">
+        <v>200</v>
+      </c>
+      <c r="G24" s="14">
+        <v>4</v>
+      </c>
+      <c r="H24" s="14">
+        <v>200</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+        <v>480</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBA958D2-E0C4-4AF0-B87C-EB7BB36D054C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57A4B4B6-531F-42E4-807B-F14BB8317B20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -254,6 +254,9 @@
   </si>
   <si>
     <t>today something new  learning</t>
+  </si>
+  <si>
+    <t>good day</t>
   </si>
 </sst>
 </file>
@@ -1907,26 +1910,50 @@
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="A25" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B25" s="14">
+        <v>500</v>
+      </c>
+      <c r="C25" s="14">
+        <v>30</v>
+      </c>
+      <c r="D25" s="14">
+        <v>40</v>
+      </c>
+      <c r="E25" s="14">
+        <v>15</v>
+      </c>
+      <c r="F25" s="14">
+        <v>0</v>
+      </c>
+      <c r="G25" s="14">
+        <v>0</v>
+      </c>
+      <c r="H25" s="14">
+        <v>300</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>885</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+        <v>555</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57A4B4B6-531F-42E4-807B-F14BB8317B20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C02A4838-DDE2-4BC2-BD6B-F3D34BF234D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1956,26 +1956,50 @@
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B26" s="14">
+        <v>480</v>
+      </c>
+      <c r="C26" s="14">
+        <v>30</v>
+      </c>
+      <c r="D26" s="14">
+        <v>50</v>
+      </c>
+      <c r="E26" s="14">
+        <v>25</v>
+      </c>
+      <c r="F26" s="14">
+        <v>0</v>
+      </c>
+      <c r="G26" s="14">
+        <v>0</v>
+      </c>
+      <c r="H26" s="14">
+        <v>260</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>845</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+        <v>595</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C02A4838-DDE2-4BC2-BD6B-F3D34BF234D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEAF86A1-4051-4653-BAA7-6C72F2BC52CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -257,6 +257,12 @@
   </si>
   <si>
     <t>good day</t>
+  </si>
+  <si>
+    <t>Stressed</t>
+  </si>
+  <si>
+    <t>bad day</t>
   </si>
 </sst>
 </file>
@@ -2002,26 +2008,50 @@
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="A27" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B27" s="14">
+        <v>360</v>
+      </c>
+      <c r="C27" s="14">
+        <v>20</v>
+      </c>
+      <c r="D27" s="14">
+        <v>40</v>
+      </c>
+      <c r="E27" s="14">
+        <v>25</v>
+      </c>
+      <c r="F27" s="14">
+        <v>300</v>
+      </c>
+      <c r="G27" s="14">
+        <v>6</v>
+      </c>
+      <c r="H27" s="14">
+        <v>250</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>995</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>445</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEAF86A1-4051-4653-BAA7-6C72F2BC52CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{907AE4E7-8CCE-40FF-8FA7-548C82D129FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2054,26 +2054,50 @@
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B28" s="14">
+        <v>360</v>
+      </c>
+      <c r="C28" s="14">
+        <v>25</v>
+      </c>
+      <c r="D28" s="14">
+        <v>20</v>
+      </c>
+      <c r="E28" s="14">
+        <v>30</v>
+      </c>
+      <c r="F28" s="14">
+        <v>350</v>
+      </c>
+      <c r="G28" s="14">
+        <v>7</v>
+      </c>
+      <c r="H28" s="14">
+        <v>200</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>985</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+        <v>455</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{907AE4E7-8CCE-40FF-8FA7-548C82D129FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A71C0072-73DB-4AC6-8318-58FA34CE0D8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2100,26 +2100,50 @@
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B29" s="14">
+        <v>420</v>
+      </c>
+      <c r="C29" s="14">
+        <v>20</v>
+      </c>
+      <c r="D29" s="14">
+        <v>50</v>
+      </c>
+      <c r="E29" s="14">
+        <v>30</v>
+      </c>
+      <c r="F29" s="14">
+        <v>6</v>
+      </c>
+      <c r="G29" s="14">
+        <v>360</v>
+      </c>
+      <c r="H29" s="14">
+        <v>230</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>756</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+        <v>684</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A71C0072-73DB-4AC6-8318-58FA34CE0D8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1EC04D0-68FE-432E-AA99-C895F84FDAE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -263,6 +263,9 @@
   </si>
   <si>
     <t>bad day</t>
+  </si>
+  <si>
+    <t>good feeling for today</t>
   </si>
 </sst>
 </file>
@@ -2146,26 +2149,50 @@
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B30" s="14">
+        <v>400</v>
+      </c>
+      <c r="C30" s="14">
+        <v>30</v>
+      </c>
+      <c r="D30" s="14">
+        <v>120</v>
+      </c>
+      <c r="E30" s="14">
+        <v>30</v>
+      </c>
+      <c r="F30" s="14">
+        <v>150</v>
+      </c>
+      <c r="G30" s="14">
+        <v>3</v>
+      </c>
+      <c r="H30" s="14">
+        <v>300</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>410</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1EC04D0-68FE-432E-AA99-C895F84FDAE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4282A7D-4D43-456D-858F-9C03F96FDEB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2195,26 +2195,50 @@
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="A31" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B31" s="14">
+        <v>350</v>
+      </c>
+      <c r="C31" s="14">
+        <v>20</v>
+      </c>
+      <c r="D31" s="14">
+        <v>50</v>
+      </c>
+      <c r="E31" s="14">
+        <v>20</v>
+      </c>
+      <c r="F31" s="14">
+        <v>250</v>
+      </c>
+      <c r="G31" s="14">
+        <v>5</v>
+      </c>
+      <c r="H31" s="14">
+        <v>250</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>940</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+        <v>500</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4282A7D-4D43-456D-858F-9C03F96FDEB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA0DDE9E-2EFB-4D36-B58C-B90357F210C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2241,26 +2241,50 @@
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="A32" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B32" s="14">
+        <v>480</v>
+      </c>
+      <c r="C32" s="14">
+        <v>30</v>
+      </c>
+      <c r="D32" s="14">
+        <v>30</v>
+      </c>
+      <c r="E32" s="14">
+        <v>20</v>
+      </c>
+      <c r="F32" s="14">
+        <v>0</v>
+      </c>
+      <c r="G32" s="14">
+        <v>0</v>
+      </c>
+      <c r="H32" s="14">
+        <v>300</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>860</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+        <v>580</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" s="13"/>
